--- a/作业互评打分表_已填写.xlsx
+++ b/作业互评打分表_已填写.xlsx
@@ -1721,30 +1721,12 @@
           <t>绝柳℡</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>"真正拉开差距的，不是AI，是你看不出哪里烂"——约3页，写得清晰有洞察力，判断力/反馈系统/审美的角度好。不足：篇幅太短，更像一篇短文</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>100句分11个主题类别（语言·自我·注意力等），格式清晰干净，保留原话。不足：缺乏分级体系或筛选方法论说明</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>标题极其犀利——"你缺的不是文案模板，是脑子里没有可卖的判断""越想火的人三年后废得越快"，每个选题配100-200字正文段落，传播力强</t>
-        </is>
-      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="8" t="n"/>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="inlineStr">

--- a/作业互评打分表_已填写.xlsx
+++ b/作业互评打分表_已填写.xlsx
@@ -724,7 +724,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -752,6 +752,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1721,12 +1724,30 @@
           <t>绝柳℡</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="8" t="n"/>
+      <c r="B22" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>极其出色。116页四部八章的完整著作，标题'28岁，从废墟里捡说明书的人'精准概括全书。基于150万字社群语料做深度思想解剖，结构严谨：从三层工具论→语言暴政→心理X光片→组织设计→AI Native组织，层层递进。写作非常成熟，开篇用直播场景切入，节奏感强；【分析者】插件提供多视角批判性思考，如'自恋还是自省'段落展现高度思辨力。终章'同时成立的判断'——在乎与控制并非矛盾而是一体两面——体现了超越二元对立的认知深度。不足：部分章节篇幅过长，中后段信息密度略有下降。整体是所有书/文章提交中最有深度和完成度的作品之一。</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>组织清晰，100条金句分为11个主题章节（三层工具论、语言系统、注意力主权、审美、复利、结构与叙事、人性与信任、组织与制度、AI与未来、自我与成长、价值观与世界），覆盖面广。每条标注日期可回源检索，体现严谨的编选态度。选句质量高，如'你的语言我只是脑区里面很小的一个部分'等句深入本质。不足：缺少使用场景标注（如适用于哪类内容/平台），没有编选方法论说明，相比有类型+使用标注的版本，实操指导性稍弱。</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>极其系统的'迭代增强版'，25页。亮点突出：①优先级矩阵用传播力(星级)×难度(ABC)量化排序，决策依据清晰；②每个选题配完整内容骨架——30字内开头钩子、3核心论点、反转/争议点、结尾行动号召，直接可执行；③三平台变体（公众号长文/抖音长文/小红书图文）针对性适配；④90天选题发布日历，按周排布平台轮换节奏。选题本身极具传播力，如'给脑区当狗''深夜emo是血糖问题''不信人性信AI'等切中痛点。是所有选题中操作性最强、系统化程度最高的作品，堪称标杆。</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
